--- a/notes/challenges/challenge-schedule.xlsx
+++ b/notes/challenges/challenge-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeff/Documents/code/script-survivor/notes/challenges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57D58EE-E963-7244-94A4-B856DC174614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D888E94-4955-E048-89CF-093E4A52A8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="920" windowWidth="18440" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14780" yWindow="920" windowWidth="14480" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Challenge Schedule" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
   <si>
     <t>EP. 13</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Weapon Adornment</t>
+  </si>
+  <si>
+    <t>Ledge Endurance</t>
+  </si>
+  <si>
+    <t>Blindfold Tree Maze</t>
   </si>
 </sst>
 </file>
@@ -278,8 +284,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -291,6 +295,8 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,19 +618,19 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -634,11 +640,11 @@
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
@@ -649,135 +655,135 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
-      <c r="B9" s="15"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
-      <c r="B12" s="15"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
-      <c r="B15" s="15"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
-      <c r="B18" s="15"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
-      <c r="B21" s="15"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -787,11 +793,11 @@
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
@@ -805,16 +811,16 @@
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -827,19 +833,19 @@
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -852,19 +858,19 @@
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -880,16 +886,16 @@
       <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -905,7 +911,7 @@
       <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -921,7 +927,7 @@
       <c r="B40" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="10" t="s">
         <v>19</v>
       </c>
     </row>
